--- a/templates/com_v1_params_template.xlsx
+++ b/templates/com_v1_params_template.xlsx
@@ -430,7 +430,7 @@
         </is>
       </c>
       <c r="C4" s="13" t="n">
-        <v>106250000000</v>
+        <v>53125000000</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>61624999999.99999</v>
+        <v>30812500000</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>1328125000</v>
+        <v>664062500</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="C63" s="13" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="C77" s="13" t="n">
-        <v>1</v>
+        <v>0.99999</v>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>

--- a/templates/com_v1_params_template.xlsx
+++ b/templates/com_v1_params_template.xlsx
@@ -374,7 +374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.63000011444092" customWidth="1" style="3" min="1" max="1"/>
@@ -419,152 +419,158 @@
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="3">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>fb</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="n">
-        <v>53125000000</v>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Hz</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Signaling rate / baud rate.</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>case</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>case_id</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>debug_case_93a_style</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>93A-style smoke/debug case; not a formal IEEE 93A validation case.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="3">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>per_ui</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="n">
-        <v>64</v>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>samples/UI</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Oversampling ratio M.</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>case</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>case_source</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>pychopmarg_8023dj_example2</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Original channel/config family is PyChOpMarg IEEE 802.3dj example2.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="3">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>target_df</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Hz</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Target frequency step.</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>case</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>case_warning</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Uses 802.3dj example channels with fb forced to 53.125e9 for debug only.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Do not use this workbook as an official 93A reference/correlation baseline.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="3">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>link</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>c_m3</t>
+          <t>fb</t>
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0</v>
+        <v>53125000000</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>dimensionless</t>
+          <t>Hz</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>TX FFE c(-3), fixed default for single run.</t>
+          <t>Signaling rate / baud rate.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="3">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>link</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>c_m2</t>
+          <t>per_ui</t>
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>dimensionless</t>
+          <t>samples/UI</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>TX FFE c(-2), fixed default if no search.</t>
+          <t>Oversampling ratio M.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="3">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>link</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>c_m1</t>
+          <t>target_df</t>
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>0</v>
+        <v>50000000</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>dimensionless</t>
+          <t>Hz</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>TX FFE c(-1), fixed default if no search.</t>
+          <t>Target frequency step.</t>
         </is>
       </c>
     </row>
@@ -576,7 +582,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>c_1</t>
+          <t>c_m3</t>
         </is>
       </c>
       <c r="C10" s="13" t="n">
@@ -589,7 +595,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>TX FFE c(1), fixed default if no search.</t>
+          <t>TX FFE c(-3), fixed default for single run.</t>
         </is>
       </c>
     </row>
@@ -601,20 +607,20 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>num_pre</t>
+          <t>c_m2</t>
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>tap index</t>
+          <t>dimensionless</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Main cursor index in TX FFE vector.</t>
+          <t>TX FFE c(-2), fixed default if no search.</t>
         </is>
       </c>
     </row>
@@ -626,20 +632,20 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Tr</t>
+          <t>c_m1</t>
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>4e-12</v>
+        <v>0</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>dimensionless</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>20%-80% transition time.</t>
+          <t>TX FFE c(-1), fixed default if no search.</t>
         </is>
       </c>
     </row>
@@ -651,20 +657,20 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>c_1</t>
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>30812500000</v>
+        <v>0</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Hz</t>
+          <t>dimensionless</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Receiver noise-filter 3 dB bandwidth.</t>
+          <t>TX FFE c(1), fixed default if no search.</t>
         </is>
       </c>
     </row>
@@ -676,20 +682,20 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>g_DC</t>
+          <t>num_pre</t>
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>dB</t>
+          <t>tap index</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>CTLE DC gain default if no search.</t>
+          <t>Main cursor index in TX FFE vector.</t>
         </is>
       </c>
     </row>
@@ -701,20 +707,20 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>g_DC2</t>
+          <t>Tr</t>
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>0</v>
+        <v>4e-12</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>dB</t>
+          <t>s</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>CTLE second DC gain default if no search.</t>
+          <t>20%-80% transition time.</t>
         </is>
       </c>
     </row>
@@ -726,11 +732,11 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>f_z</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>1000000000000</v>
+        <v>30812500000</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
@@ -739,7 +745,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>CTLE zero frequency.</t>
+          <t>Receiver noise-filter 3 dB bandwidth.</t>
         </is>
       </c>
     </row>
@@ -751,20 +757,20 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>f_LF</t>
+          <t>g_DC</t>
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>664062500</v>
+        <v>2</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Hz</t>
+          <t>dB</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Low-frequency pole/zero term.</t>
+          <t>CTLE DC gain default if no search.</t>
         </is>
       </c>
     </row>
@@ -776,20 +782,20 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>f_p1</t>
+          <t>g_DC2</t>
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>1000000000000</v>
+        <v>0</v>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Hz</t>
+          <t>dB</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>CTLE pole 1.</t>
+          <t>CTLE second DC gain default if no search.</t>
         </is>
       </c>
     </row>
@@ -801,7 +807,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>f_p2</t>
+          <t>f_z</t>
         </is>
       </c>
       <c r="C19" s="13" t="n">
@@ -814,7 +820,7 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>CTLE pole 2.</t>
+          <t>CTLE zero frequency.</t>
         </is>
       </c>
     </row>
@@ -826,20 +832,20 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>A_v</t>
+          <t>f_LF</t>
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>0.413</v>
+        <v>664062500</v>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>Hz</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>Victim pulse amplitude.</t>
+          <t>Low-frequency pole/zero term.</t>
         </is>
       </c>
     </row>
@@ -851,20 +857,20 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>A_fe</t>
+          <t>f_p1</t>
         </is>
       </c>
       <c r="C21" s="13" t="n">
-        <v>0.413</v>
+        <v>1000000000000</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>Hz</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>FEXT aggressor pulse amplitude.</t>
+          <t>CTLE pole 1.</t>
         </is>
       </c>
     </row>
@@ -876,95 +882,95 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
+          <t>f_p2</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>1000000000000</v>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>CTLE pole 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="3">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>A_v</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>Victim pulse amplitude.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="3">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>A_fe</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>FEXT aggressor pulse amplitude.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="3">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
           <t>A_ne</t>
         </is>
       </c>
-      <c r="C22" s="13" t="n">
+      <c r="C25" s="13" t="n">
         <v>0.45</v>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>NEXT aggressor pulse amplitude.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="3">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>txpkg_victim</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>txpkg_victim.enable</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Enable Victim TX package model.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="3">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>txpkg_victim</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>txpkg_victim.C_d</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="n">
-        <v>4e-14</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Victim TX device shunt capacitance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="3">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>txpkg_victim</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>txpkg_victim.L_s</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="n">
-        <v>1.3e-10</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Victim TX series inductance.</t>
         </is>
       </c>
     </row>
@@ -976,20 +982,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>txpkg_victim.C_b</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="n">
-        <v>3e-14</v>
+          <t>txpkg_victim.enable</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="b">
+        <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Victim TX bump/interface shunt capacitance.</t>
+          <t>Enable Victim TX package model.</t>
         </is>
       </c>
     </row>
@@ -1001,20 +1007,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>txpkg_victim.z_p</t>
+          <t>txpkg_victim.C_d</t>
         </is>
       </c>
       <c r="C27" s="14" t="n">
-        <v>34</v>
+        <v>4e-14</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Victim TX package transmission-line length.</t>
+          <t>Victim TX device shunt capacitance.</t>
         </is>
       </c>
     </row>
@@ -1026,20 +1032,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>txpkg_victim.C_p</t>
+          <t>txpkg_victim.L_s</t>
         </is>
       </c>
       <c r="C28" s="14" t="n">
-        <v>4e-14</v>
+        <v>1.3e-10</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Victim TX package-to-board shunt capacitance.</t>
+          <t>Victim TX series inductance.</t>
         </is>
       </c>
     </row>
@@ -1051,20 +1057,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>txpkg_victim.R0</t>
+          <t>txpkg_victim.C_b</t>
         </is>
       </c>
       <c r="C29" s="14" t="n">
-        <v>50</v>
+        <v>3e-14</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ohm</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Victim TX single-ended reference resistance.</t>
+          <t>Victim TX bump/interface shunt capacitance.</t>
         </is>
       </c>
     </row>
@@ -1076,20 +1082,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>txpkg_victim.Z_c</t>
+          <t>txpkg_victim.z_p</t>
         </is>
       </c>
       <c r="C30" s="14" t="n">
-        <v>87.5</v>
+        <v>34</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ohm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Victim TX differential characteristic impedance.</t>
+          <t>Victim TX package transmission-line length.</t>
         </is>
       </c>
     </row>
@@ -1101,18 +1107,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>txpkg_victim.z_p2</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="n"/>
+          <t>txpkg_victim.C_p</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>4e-14</v>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Victim TX optional package TL segment 2. Blank means disabled.</t>
+          <t>Victim TX package-to-board shunt capacitance.</t>
         </is>
       </c>
     </row>
@@ -1124,11 +1132,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>txpkg_victim.Z_c2</t>
+          <t>txpkg_victim.R0</t>
         </is>
       </c>
       <c r="C32" s="14" t="n">
-        <v>87.5</v>
+        <v>50</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1137,82 +1145,80 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Victim TX optional segment 2 differential impedance.</t>
+          <t>Victim TX single-ended reference resistance.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="3">
       <c r="A33" t="inlineStr">
         <is>
-          <t>txpkg_fext</t>
+          <t>txpkg_victim</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>txpkg_fext.enable</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="b">
-        <v>1</v>
+          <t>txpkg_victim.Z_c</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>87.5</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>ohm</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Enable FEXT TX package model.</t>
+          <t>Victim TX differential characteristic impedance.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="3">
       <c r="A34" t="inlineStr">
         <is>
-          <t>txpkg_fext</t>
+          <t>txpkg_victim</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>txpkg_fext.C_d</t>
-        </is>
-      </c>
-      <c r="C34" s="14" t="n">
-        <v>4e-14</v>
-      </c>
+          <t>txpkg_victim.z_p2</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="n"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FEXT TX device shunt capacitance.</t>
+          <t>Victim TX optional package TL segment 2. Blank means disabled.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="3">
       <c r="A35" t="inlineStr">
         <is>
-          <t>txpkg_fext</t>
+          <t>txpkg_victim</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>txpkg_fext.L_s</t>
+          <t>txpkg_victim.Z_c2</t>
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>1.3e-10</v>
+        <v>87.5</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>ohm</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FEXT TX series inductance.</t>
+          <t>Victim TX optional segment 2 differential impedance.</t>
         </is>
       </c>
     </row>
@@ -1224,20 +1230,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>txpkg_fext.C_b</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="n">
-        <v>3e-14</v>
+          <t>txpkg_fext.enable</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="b">
+        <v>1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FEXT TX bump/interface shunt capacitance.</t>
+          <t>Enable FEXT TX package model.</t>
         </is>
       </c>
     </row>
@@ -1249,20 +1255,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>txpkg_fext.z_p</t>
+          <t>txpkg_fext.C_d</t>
         </is>
       </c>
       <c r="C37" s="14" t="n">
-        <v>34</v>
+        <v>4e-14</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FEXT TX package transmission-line length.</t>
+          <t>FEXT TX device shunt capacitance.</t>
         </is>
       </c>
     </row>
@@ -1274,20 +1280,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>txpkg_fext.C_p</t>
+          <t>txpkg_fext.L_s</t>
         </is>
       </c>
       <c r="C38" s="14" t="n">
-        <v>4e-14</v>
+        <v>1.3e-10</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FEXT TX package-to-board shunt capacitance.</t>
+          <t>FEXT TX series inductance.</t>
         </is>
       </c>
     </row>
@@ -1299,20 +1305,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>txpkg_fext.R0</t>
+          <t>txpkg_fext.C_b</t>
         </is>
       </c>
       <c r="C39" s="14" t="n">
-        <v>50</v>
+        <v>3e-14</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ohm</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FEXT TX single-ended reference resistance.</t>
+          <t>FEXT TX bump/interface shunt capacitance.</t>
         </is>
       </c>
     </row>
@@ -1324,20 +1330,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>txpkg_fext.Z_c</t>
+          <t>txpkg_fext.z_p</t>
         </is>
       </c>
       <c r="C40" s="14" t="n">
-        <v>87.5</v>
+        <v>34</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ohm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FEXT TX differential characteristic impedance.</t>
+          <t>FEXT TX package transmission-line length.</t>
         </is>
       </c>
     </row>
@@ -1349,18 +1355,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>txpkg_fext.z_p2</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="n"/>
+          <t>txpkg_fext.C_p</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="n">
+        <v>4e-14</v>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FEXT TX optional package TL segment 2. Blank means disabled.</t>
+          <t>FEXT TX package-to-board shunt capacitance.</t>
         </is>
       </c>
     </row>
@@ -1372,11 +1380,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>txpkg_fext.Z_c2</t>
+          <t>txpkg_fext.R0</t>
         </is>
       </c>
       <c r="C42" s="14" t="n">
-        <v>87.5</v>
+        <v>50</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1385,82 +1393,80 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FEXT TX optional segment 2 differential impedance.</t>
+          <t>FEXT TX single-ended reference resistance.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="3">
       <c r="A43" t="inlineStr">
         <is>
-          <t>txpkg_next</t>
+          <t>txpkg_fext</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>txpkg_next.enable</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="b">
-        <v>1</v>
+          <t>txpkg_fext.Z_c</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="n">
+        <v>87.5</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>ohm</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Enable NEXT TX package model.</t>
+          <t>FEXT TX differential characteristic impedance.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="3">
       <c r="A44" t="inlineStr">
         <is>
-          <t>txpkg_next</t>
+          <t>txpkg_fext</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>txpkg_next.C_d</t>
-        </is>
-      </c>
-      <c r="C44" s="14" t="n">
-        <v>4e-14</v>
-      </c>
+          <t>txpkg_fext.z_p2</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="n"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>NEXT TX device shunt capacitance.</t>
+          <t>FEXT TX optional package TL segment 2. Blank means disabled.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="3">
       <c r="A45" t="inlineStr">
         <is>
-          <t>txpkg_next</t>
+          <t>txpkg_fext</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>txpkg_next.L_s</t>
+          <t>txpkg_fext.Z_c2</t>
         </is>
       </c>
       <c r="C45" s="14" t="n">
-        <v>1.3e-10</v>
+        <v>87.5</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>ohm</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>NEXT TX series inductance.</t>
+          <t>FEXT TX optional segment 2 differential impedance.</t>
         </is>
       </c>
     </row>
@@ -1472,20 +1478,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>txpkg_next.C_b</t>
-        </is>
-      </c>
-      <c r="C46" s="14" t="n">
-        <v>3e-14</v>
+          <t>txpkg_next.enable</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="b">
+        <v>1</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>NEXT TX bump/interface shunt capacitance.</t>
+          <t>Enable NEXT TX package model.</t>
         </is>
       </c>
     </row>
@@ -1497,20 +1503,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>txpkg_next.z_p</t>
+          <t>txpkg_next.C_d</t>
         </is>
       </c>
       <c r="C47" s="14" t="n">
-        <v>34</v>
+        <v>4e-14</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>NEXT TX package transmission-line length.</t>
+          <t>NEXT TX device shunt capacitance.</t>
         </is>
       </c>
     </row>
@@ -1522,20 +1528,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>txpkg_next.C_p</t>
+          <t>txpkg_next.L_s</t>
         </is>
       </c>
       <c r="C48" s="14" t="n">
-        <v>4e-14</v>
+        <v>1.3e-10</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>NEXT TX package-to-board shunt capacitance.</t>
+          <t>NEXT TX series inductance.</t>
         </is>
       </c>
     </row>
@@ -1547,20 +1553,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>txpkg_next.R0</t>
+          <t>txpkg_next.C_b</t>
         </is>
       </c>
       <c r="C49" s="14" t="n">
-        <v>50</v>
+        <v>3e-14</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ohm</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>NEXT TX single-ended reference resistance.</t>
+          <t>NEXT TX bump/interface shunt capacitance.</t>
         </is>
       </c>
     </row>
@@ -1572,20 +1578,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>txpkg_next.Z_c</t>
+          <t>txpkg_next.z_p</t>
         </is>
       </c>
       <c r="C50" s="14" t="n">
-        <v>87.5</v>
+        <v>34</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ohm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>NEXT TX differential characteristic impedance.</t>
+          <t>NEXT TX package transmission-line length.</t>
         </is>
       </c>
     </row>
@@ -1597,18 +1603,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>txpkg_next.z_p2</t>
-        </is>
-      </c>
-      <c r="C51" s="14" t="n"/>
+          <t>txpkg_next.C_p</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="n">
+        <v>4e-14</v>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>NEXT TX optional package TL segment 2. Blank means disabled.</t>
+          <t>NEXT TX package-to-board shunt capacitance.</t>
         </is>
       </c>
     </row>
@@ -1620,11 +1628,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>txpkg_next.Z_c2</t>
+          <t>txpkg_next.R0</t>
         </is>
       </c>
       <c r="C52" s="14" t="n">
-        <v>87.5</v>
+        <v>50</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1633,82 +1641,80 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>NEXT TX optional segment 2 differential impedance.</t>
+          <t>NEXT TX single-ended reference resistance.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" s="3">
       <c r="A53" t="inlineStr">
         <is>
-          <t>rxpkg</t>
+          <t>txpkg_next</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>rxpkg.enable</t>
-        </is>
-      </c>
-      <c r="C53" s="14" t="b">
-        <v>1</v>
+          <t>txpkg_next.Z_c</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="n">
+        <v>87.5</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>ohm</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Enable RX package model.</t>
+          <t>NEXT TX differential characteristic impedance.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="3">
       <c r="A54" t="inlineStr">
         <is>
-          <t>rxpkg</t>
+          <t>txpkg_next</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>rxpkg.C_d</t>
-        </is>
-      </c>
-      <c r="C54" s="14" t="n">
-        <v>4e-14</v>
-      </c>
+          <t>txpkg_next.z_p2</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="n"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RX device shunt capacitance.</t>
+          <t>NEXT TX optional package TL segment 2. Blank means disabled.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="3">
       <c r="A55" t="inlineStr">
         <is>
-          <t>rxpkg</t>
+          <t>txpkg_next</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>rxpkg.L_s</t>
+          <t>txpkg_next.Z_c2</t>
         </is>
       </c>
       <c r="C55" s="14" t="n">
-        <v>1.3e-10</v>
+        <v>87.5</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>ohm</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RX series inductance.</t>
+          <t>NEXT TX optional segment 2 differential impedance.</t>
         </is>
       </c>
     </row>
@@ -1720,20 +1726,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>rxpkg.C_b</t>
-        </is>
-      </c>
-      <c r="C56" s="14" t="n">
-        <v>3e-14</v>
+          <t>rxpkg.enable</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="b">
+        <v>1</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RX bump/interface shunt capacitance.</t>
+          <t>Enable RX package model.</t>
         </is>
       </c>
     </row>
@@ -1745,20 +1751,20 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>rxpkg.z_p</t>
+          <t>rxpkg.C_d</t>
         </is>
       </c>
       <c r="C57" s="14" t="n">
-        <v>34</v>
+        <v>4e-14</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RX package transmission-line length.</t>
+          <t>RX device shunt capacitance.</t>
         </is>
       </c>
     </row>
@@ -1770,20 +1776,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>rxpkg.C_p</t>
+          <t>rxpkg.L_s</t>
         </is>
       </c>
       <c r="C58" s="14" t="n">
-        <v>4e-14</v>
+        <v>1.3e-10</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RX package-to-board shunt capacitance.</t>
+          <t>RX series inductance.</t>
         </is>
       </c>
     </row>
@@ -1795,20 +1801,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>rxpkg.R0</t>
+          <t>rxpkg.C_b</t>
         </is>
       </c>
       <c r="C59" s="14" t="n">
-        <v>50</v>
+        <v>3e-14</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ohm</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RX single-ended reference resistance.</t>
+          <t>RX bump/interface shunt capacitance.</t>
         </is>
       </c>
     </row>
@@ -1820,20 +1826,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>rxpkg.Z_c</t>
+          <t>rxpkg.z_p</t>
         </is>
       </c>
       <c r="C60" s="14" t="n">
-        <v>87.5</v>
+        <v>34</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ohm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RX differential characteristic impedance.</t>
+          <t>RX package transmission-line length.</t>
         </is>
       </c>
     </row>
@@ -1845,18 +1851,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>rxpkg.z_p2</t>
-        </is>
-      </c>
-      <c r="C61" s="14" t="n"/>
+          <t>rxpkg.C_p</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="n">
+        <v>4e-14</v>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RX optional package TL segment 2. Blank means disabled.</t>
+          <t>RX package-to-board shunt capacitance.</t>
         </is>
       </c>
     </row>
@@ -1868,145 +1876,143 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>rxpkg.R0</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ohm</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RX single-ended reference resistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>rxpkg</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>rxpkg.Z_c</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ohm</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RX differential characteristic impedance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>rxpkg</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>rxpkg.z_p2</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="n"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RX optional package TL segment 2. Blank means disabled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>rxpkg</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>rxpkg.Z_c2</t>
         </is>
       </c>
-      <c r="C62" s="14" t="n">
+      <c r="C65" s="14" t="n">
         <v>87.5</v>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>ohm</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>RX optional segment 2 differential impedance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>dfe</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>N_b</t>
-        </is>
-      </c>
-      <c r="C63" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>UI/taps</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>Fixed DFE tap count.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>dfe</t>
-        </is>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>b_max</t>
-        </is>
-      </c>
-      <c r="C64" s="13" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>dimensionless</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>Normalized fixed DFE coefficient limit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>impairment</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>R_LM</t>
-        </is>
-      </c>
-      <c r="C65" s="13" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>dimensionless</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>Level separation mismatch ratio.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>impairment</t>
+          <t>dfe</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>SNR_TX</t>
+          <t>N_b</t>
         </is>
       </c>
       <c r="C66" s="13" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>dB</t>
+          <t>UI/taps</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>Transmitter SNR.</t>
+          <t>Fixed DFE tap count.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>impairment</t>
+          <t>dfe</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>sigma_RJ</t>
+          <t>b_max</t>
         </is>
       </c>
       <c r="C67" s="13" t="n">
-        <v>0.01</v>
+        <v>0.85</v>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>dimensionless</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>Random jitter RMS.</t>
+          <t>Normalized fixed DFE coefficient limit.</t>
         </is>
       </c>
     </row>
@@ -2018,20 +2024,20 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>A_DD</t>
+          <t>R_LM</t>
         </is>
       </c>
       <c r="C68" s="13" t="n">
-        <v>0.02</v>
+        <v>0.95</v>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>dimensionless</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>Dual-Dirac jitter peak.</t>
+          <t>Level separation mismatch ratio.</t>
         </is>
       </c>
     </row>
@@ -2043,143 +2049,145 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>eta_0</t>
+          <t>SNR_TX</t>
         </is>
       </c>
       <c r="C69" s="13" t="n">
-        <v>6e-18</v>
+        <v>33</v>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>V^2/Hz</t>
+          <t>dB</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>One-sided noise spectral density.</t>
+          <t>Transmitter SNR.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>com</t>
+          <t>impairment</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>sigma_RJ</t>
         </is>
       </c>
       <c r="C70" s="13" t="n">
-        <v>4</v>
+        <v>0.01</v>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>levels</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>Number of signal levels.</t>
+          <t>Random jitter RMS.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>com</t>
+          <t>impairment</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>DER_0</t>
+          <t>A_DD</t>
         </is>
       </c>
       <c r="C71" s="13" t="n">
-        <v>0.0002</v>
+        <v>0.02</v>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>dimensionless</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>Target detector error ratio.</t>
+          <t>Dual-Dirac jitter peak.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>pmf</t>
+          <t>impairment</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>dy_override</t>
-        </is>
-      </c>
-      <c r="C72" s="13" t="str"/>
+          <t>eta_0</t>
+        </is>
+      </c>
+      <c r="C72" s="13" t="n">
+        <v>6e-18</v>
+      </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>V^2/Hz</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>Blank means derive from As.</t>
+          <t>One-sided noise spectral density.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>pmf</t>
+          <t>com</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>dy_rel_As</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C73" s="13" t="n">
-        <v>0.001</v>
+        <v>4</v>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>dimensionless</t>
+          <t>levels</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>PMF dy relative to As.</t>
+          <t>Number of signal levels.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>pmf</t>
+          <t>com</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>dy_abs_max</t>
+          <t>DER_0</t>
         </is>
       </c>
       <c r="C74" s="13" t="n">
-        <v>1e-05</v>
+        <v>0.0002</v>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>dimensionless</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>PMF dy absolute maximum.</t>
+          <t>Target detector error ratio.</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2199,7 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>tap_abs_th_override</t>
+          <t>dy_override</t>
         </is>
       </c>
       <c r="C75" s="13" t="str"/>
@@ -2214,7 +2222,7 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>tap_rel_As</t>
+          <t>dy_rel_As</t>
         </is>
       </c>
       <c r="C76" s="13" t="n">
@@ -2227,7 +2235,7 @@
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>Tap threshold relative to As.</t>
+          <t>PMF dy relative to As.</t>
         </is>
       </c>
     </row>
@@ -2239,20 +2247,20 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>keep_mass</t>
+          <t>dy_abs_max</t>
         </is>
       </c>
       <c r="C77" s="13" t="n">
-        <v>0.99999</v>
+        <v>1e-05</v>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>probability</t>
+          <t>V</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>PMF truncation target.</t>
+          <t>PMF dy absolute maximum.</t>
         </is>
       </c>
     </row>
@@ -2264,31 +2272,95 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
+          <t>tap_abs_th_override</t>
+        </is>
+      </c>
+      <c r="C78" s="13" t="str"/>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>Blank means derive from As.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>pmf</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>tap_rel_As</t>
+        </is>
+      </c>
+      <c r="C79" s="13" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>dimensionless</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>Tap threshold relative to As.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>pmf</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>keep_mass</t>
+        </is>
+      </c>
+      <c r="C80" s="13" t="n">
+        <v>0.99999</v>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>probability</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>PMF truncation target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>pmf</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
           <t>gaussian_n_sigma</t>
         </is>
       </c>
-      <c r="C78" s="13" t="n">
+      <c r="C81" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="D78" s="7" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>sigma</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t>Gaussian PMF half span.</t>
         </is>
       </c>
-    </row>
-    <row r="79">
-      <c r="C79" s="14" t="n"/>
-    </row>
-    <row r="80">
-      <c r="C80" s="14" t="n"/>
-    </row>
-    <row r="81">
-      <c r="C81" s="14" t="n"/>
     </row>
     <row r="82">
       <c r="C82" s="14" t="n"/>
@@ -2316,6 +2388,15 @@
     </row>
     <row r="90">
       <c r="C90" s="14" t="n"/>
+    </row>
+    <row r="91">
+      <c r="C91" s="14" t="n"/>
+    </row>
+    <row r="92">
+      <c r="C92" s="14" t="n"/>
+    </row>
+    <row r="93">
+      <c r="C93" s="14" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
